--- a/content/Question Bank/MCQ/Python/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
+++ b/content/Question Bank/MCQ/Python/Unit 9 - Basic Object-Oriented Programming/Unit 9 - Basic Object-Oriented Programming - MCQ.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9" sheetId="1" r:id="R30d150b0a6fb4e88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Python - MCQ - 9" sheetId="1" r:id="R27fb7d40d5b843d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -405,15 +405,16 @@
         <x:v>16</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="18" customHeight="1">
+    <x:row r="2" ht="36" hidden="0" customHeight="1">
       <x:c r="A2" s="1" t="str">
         <x:v>Python - MCQ - 9.1.1</x:v>
       </x:c>
       <x:c r="B2" s="1" t="str">
-        <x:v>A delivery app stores each rider's name, phone number, and availability in three lists. After one phone number is removed, the records no longer match. Which redesign most directly prevents this problem?</x:v>
+        <x:v>One edit silently changes the identity of three records
+An office stores names, roll numbers, and attendance in three parallel lists. A transfer operation moves one name but not the matching values in the other lists. The program still runs, yet the next report combines facts from different students. Which redesign removes the dependency that caused the silent corruption?</x:v>
       </x:c>
       <x:c r="C2" s="2" t="str">
-        <x:v>A Rider object keeps one rider's related data together, so deleting or updating one rider does not shift an unrelated list out of alignment. The class can also hold rider-specific behavior later.</x:v>
+        <x:v>Bundling each student's related state in one object removes the positional dependency that allowed the parallel collections to drift.</x:v>
       </x:c>
       <x:c r="D2" s="4" t="n">
         <x:v>1</x:v>
@@ -422,10 +423,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F2" s="1" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G2" s="2" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H2" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -441,30 +442,31 @@
       </x:c>
       <x:c r="L2" s="1"/>
       <x:c r="M2" s="1" t="str">
-        <x:v>Sort all three lists after every change</x:v>
+        <x:v>Sort both lists independently before every report</x:v>
       </x:c>
       <x:c r="N2" s="1" t="str">
-        <x:v>Create a Rider class and store one object per rider</x:v>
+        <x:v>Add more comments explaining that the positions must match</x:v>
       </x:c>
       <x:c r="O2" s="1" t="str">
-        <x:v>Rename the lists so their purposes are clearer</x:v>
+        <x:v>Represent each student as one object carrying its related data</x:v>
       </x:c>
       <x:c r="P2" s="1" t="str">
-        <x:v>Convert only the availability list to a tuple</x:v>
+        <x:v>Convert the roll-number list into a tuple and keep the name list unchanged</x:v>
       </x:c>
       <x:c r="Q2" s="4" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="18" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="36" hidden="0" customHeight="1">
       <x:c r="A3" s="1" t="str">
         <x:v>Python - MCQ - 9.1.2</x:v>
       </x:c>
       <x:c r="B3" s="1" t="str">
-        <x:v>A game defines a `Player` class and then creates `maya = Player()`. Which description correctly identifies the two parts?</x:v>
+        <x:v>Finding the boundaries before writing classes
+A repair service must remember who raised a ticket, which technician accepted it, and how each ticket's status changes. Before choosing attributes or methods, which proposed model identifies the most defensible object boundaries?</x:v>
       </x:c>
       <x:c r="C3" s="2" t="str">
-        <x:v>`Player` is the blueprint that describes this kind of entity. `maya` refers to one specific object, also called an instance, created from that class.</x:v>
+        <x:v>`Customer`, `Technician`, and `Ticket` are the meaningful entities whose separate state and behaviour the service must model.</x:v>
       </x:c>
       <x:c r="D3" s="4" t="n">
         <x:v>1</x:v>
@@ -473,10 +475,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F3" s="1" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G3" s="2" t="str">
-        <x:v>understand</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H3" s="1" t="str">
         <x:v>python - Set 1</x:v>
@@ -488,42 +490,45 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K3" s="1" t="str">
-        <x:v>classes-and-objects</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L3" s="1"/>
       <x:c r="M3" s="1" t="str">
-        <x:v>Both names refer to classes</x:v>
+        <x:v>Identify `Customer`, `Technician`, and `Ticket` as candidate program entities</x:v>
       </x:c>
       <x:c r="N3" s="1" t="str">
-        <x:v>`maya` is the blueprint and `Player` is its attribute</x:v>
+        <x:v>Put every value into one long list, then document the position assigned to each field and entity</x:v>
       </x:c>
       <x:c r="O3" s="1" t="str">
-        <x:v>Both names refer to the same object</x:v>
+        <x:v>Create one function for each individual customer by name</x:v>
       </x:c>
       <x:c r="P3" s="1" t="str">
-        <x:v>`Player` is the class and `maya` refers to an object</x:v>
+        <x:v>Store all statuses in variables unrelated to their tickets</x:v>
       </x:c>
       <x:c r="Q3" s="4" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="211.1999969482422" hidden="0" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>Python - MCQ - 9.1.3</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>A seating app creates two bookings from the same class. A developer checks whether they are the same object.
+        <x:v>Two names may represent either one object or two
+Consider the following incident-reproduction code:
 ```python
-class Booking:
+class Parcel:
     pass
-first = Booking()
-second = Booking()
-print(first is second)
+first = Parcel()
+second = first
+third = Parcel()
+same_first_second = first is second
+same_first_third = first is third
 ```
-What does the check display?</x:v>
+Which pair is stored in `same_first_second` and `same_first_third`?</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Each call to `Booking()` creates a new object. The `is` operator checks identity, so two separately created instances are not the same object.</x:v>
+        <x:v>Assignment makes `second` an alias of `first`, while the second call to `Parcel()` creates the distinct object referenced by `third`.</x:v>
       </x:c>
       <x:c r="D4" t="n">
         <x:v>1</x:v>
@@ -532,10 +537,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F4" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G4" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H4" t="str">
         <x:v>python - Set 1</x:v>
@@ -551,356 +556,340 @@
       </x:c>
       <x:c r="L4"/>
       <x:c r="M4" t="str">
-        <x:v>False</x:v>
+        <x:v>`False, False`</x:v>
       </x:c>
       <x:c r="N4" t="str">
-        <x:v>True</x:v>
+        <x:v>`True, True`</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>Booking</x:v>
+        <x:v>`False, True`</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>An AttributeError</x:v>
+        <x:v>`True, False`</x:v>
       </x:c>
       <x:c r="Q4" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="198" hidden="0" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>Python - MCQ - 9.1.4</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>A sensor object receives only a `location` attribute, but the dashboard later asks for its `reading`.
+        <x:v>A method updates a temporary value instead of the object
+An inventory test expects `item.reserve(3)` to reduce `item.stock` from 10 to 7, but the object remains unchanged:
+```python
+class Item:
+    def reserve(self, amount):
+        stock = self.stock - amount
+item = Item()
+item.stock = 10
+item.reserve(3)
+```
+Which one-line replacement repairs the method without changing its interface?</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>Assigning through `self.stock` changes the attribute of the object that received the method call; the original line only created a local variable.</x:v>
+      </x:c>
+      <x:c r="D5" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F5" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J5" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K5" t="str">
+        <x:v>attributes-and-methods</x:v>
+      </x:c>
+      <x:c r="L5"/>
+      <x:c r="M5" t="str">
+        <x:v>`amount = self.stock - amount`</x:v>
+      </x:c>
+      <x:c r="N5" t="str">
+        <x:v>`self.stock -= amount`</x:v>
+      </x:c>
+      <x:c r="O5" t="str">
+        <x:v>`Item.stock = amount`</x:v>
+      </x:c>
+      <x:c r="P5" t="str">
+        <x:v>`return stock - amount`</x:v>
+      </x:c>
+      <x:c r="Q5" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="171.60000610351562" hidden="0" customHeight="1">
+      <x:c r="A6" t="str">
+        <x:v>Python - MCQ - 9.1.5</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>Construction succeeds only after a manual setup call
+A developer intends every new badge to receive its owner during creation, but the setup method is not recognised automatically:
+```python
+class Badge:
+    def ______(self, owner):
+        self.owner = owner
+staff_badge = Badge("Meera")
+```
+Which exact method name completes the class so that the final line succeeds?</x:v>
+      </x:c>
+      <x:c r="C6" t="str">
+        <x:v>Python invokes only the exact special method name `__init__` automatically while processing `Badge("Meera")`.</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F6" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J6" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K6" t="str">
+        <x:v>constructors</x:v>
+      </x:c>
+      <x:c r="L6"/>
+      <x:c r="M6" t="str">
+        <x:v>`_init_`</x:v>
+      </x:c>
+      <x:c r="N6" t="str">
+        <x:v>`init`</x:v>
+      </x:c>
+      <x:c r="O6" t="str">
+        <x:v>`__create__`</x:v>
+      </x:c>
+      <x:c r="P6" t="str">
+        <x:v>`__init__`</x:v>
+      </x:c>
+      <x:c r="Q6" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="224.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A7" t="str">
+        <x:v>Python - MCQ - 9.1.6</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>A shared blueprint does not imply shared state
+Two registrations are created from the same class:
+```python
+class Registration:
+    pass
+morning = Registration()
+evening = Registration()
+morning.seats = 20
+evening.seats = 35
+morning.seats -= 4
+print(morning.seats, evening.seats)
+```
+Which console record should the tester expect?</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>The subtraction changes only `morning.seats`; the independent `evening` object retains 35.</x:v>
+      </x:c>
+      <x:c r="D7" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J7" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K7" t="str">
+        <x:v>classes-and-objects</x:v>
+      </x:c>
+      <x:c r="L7"/>
+      <x:c r="M7" t="str">
+        <x:v>`16 31`</x:v>
+      </x:c>
+      <x:c r="N7" t="str">
+        <x:v>`16 35`</x:v>
+      </x:c>
+      <x:c r="O7" t="str">
+        <x:v>`20 35`</x:v>
+      </x:c>
+      <x:c r="P7" t="str">
+        <x:v>`31 31`</x:v>
+      </x:c>
+      <x:c r="Q7" t="n">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="39.599998474121094" hidden="0" customHeight="1">
+      <x:c r="A8" t="str">
+        <x:v>Python - MCQ - 9.1.7</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>Choosing a model that owns both state and a rule
+A parking application manages hundreds of lots. Each lot has its own capacity and occupied count, and every entry attempt must be rejected when that particular lot is full. Which design places the validation where it can be reused without mixing the lots' state?</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>Each object keeps one lot's state, while one shared method consistently checks that lot's capacity before changing occupancy.</x:v>
+      </x:c>
+      <x:c r="D8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J8" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K8" t="str">
+        <x:v>modeling-with-classes</x:v>
+      </x:c>
+      <x:c r="L8"/>
+      <x:c r="M8" t="str">
+        <x:v>Keep all capacities in one list and let each screen edit occupancy directly</x:v>
+      </x:c>
+      <x:c r="N8" t="str">
+        <x:v>Store each lot in a tuple and repeat the capacity check wherever an entry is recorded</x:v>
+      </x:c>
+      <x:c r="O8" t="str">
+        <x:v>Give each `ParkingLot` object its own state and an `admit` method that enforces capacity</x:v>
+      </x:c>
+      <x:c r="P8" t="str">
+        <x:v>Create one global Boolean named `has_space` and reuse it for every lot</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="145.1999969482422" hidden="0" customHeight="1">
+      <x:c r="A9" t="str">
+        <x:v>Python - MCQ - 9.1.8</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>A method accidentally consults the wrong student
+A method is supposed to judge the object receiving the call, but it uses `asha.marks` instead of `self.marks`:
+```python
+class Student:
+    def has_passed(self):
+        return asha.marks &gt;= 40
+```
+Which test data most clearly exposes the defect when the program evaluates `ravi.has_passed()`?</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>Ravi should fail with 20, but the defective method reads Asha's 80 and returns `True`; equal-side test values would conceal the wrong reference.</x:v>
+      </x:c>
+      <x:c r="D9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>hard</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>evaluate</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>python - Set 1</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J9" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K9" t="str">
+        <x:v>attributes-and-methods</x:v>
+      </x:c>
+      <x:c r="L9"/>
+      <x:c r="M9" t="str">
+        <x:v>`asha.marks = 80` and `ravi.marks = 20`</x:v>
+      </x:c>
+      <x:c r="N9" t="str">
+        <x:v>`asha.marks = 80` and `ravi.marks = 80`</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>`asha.marks = 20` and `ravi.marks = 20`</x:v>
+      </x:c>
+      <x:c r="P9" t="str">
+        <x:v>`asha.marks = 40` and `ravi.marks = 40`</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="105.5999984741211" hidden="0" customHeight="1">
+      <x:c r="A10" t="str">
+        <x:v>Python - MCQ - 9.1.9</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Completing a blueprint without inventing behaviour
+A hardware team wants an intentionally empty `Sensor` blueprint so integration code can already create `Sensor()` objects. Which completion produces a valid class while adding no premature data or behaviour?
 ```python
 class Sensor:
-    pass
-s = Sensor()
-s.location = 'Lab'
-print(s.reading)
-```
-What happens at the final line?</x:v>
-      </x:c>
-      <x:c r="C5" t="str">
-        <x:v>The object has no `reading` attribute. Accessing an attribute that was never assigned raises `AttributeError`.</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F5" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G5" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H5" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I5" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J5" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K5" t="str">
-        <x:v>attributes-and-methods</x:v>
-      </x:c>
-      <x:c r="L5"/>
-      <x:c r="M5" t="str">
-        <x:v>It prints `None`</x:v>
-      </x:c>
-      <x:c r="N5" t="str">
-        <x:v>It creates `reading` with value 0</x:v>
-      </x:c>
-      <x:c r="O5" t="str">
-        <x:v>Python raises an AttributeError</x:v>
-      </x:c>
-      <x:c r="P5" t="str">
-        <x:v>Python raises a NameError for `Sensor`</x:v>
-      </x:c>
-      <x:c r="Q5" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str">
-        <x:v>Python - MCQ - 9.1.5</x:v>
-      </x:c>
-      <x:c r="B6" t="str">
-        <x:v>A reminder class is meant to print a message, but its method was defined without `self`.
-```python
-class Reminder:
-    def show():
-        print('Submit report')
-r = Reminder()
-r.show()
-```
-Why does the call fail?</x:v>
-      </x:c>
-      <x:c r="C6" t="str">
-        <x:v>Calling an instance method automatically supplies the object as the first argument. Because `show` declares no parameter to receive it, Python raises `TypeError`.</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F6" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G6" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H6" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I6" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J6" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K6" t="str">
-        <x:v>attributes-and-methods</x:v>
-      </x:c>
-      <x:c r="L6"/>
-      <x:c r="M6" t="str">
-        <x:v>The message must be stored in an attribute first</x:v>
-      </x:c>
-      <x:c r="N6" t="str">
-        <x:v>The object is passed automatically, but `show` has no parameter for it</x:v>
-      </x:c>
-      <x:c r="O6" t="str">
-        <x:v>A method cannot print text directly</x:v>
-      </x:c>
-      <x:c r="P6" t="str">
-        <x:v>The class needs a `pass` statement after the method</x:v>
-      </x:c>
-      <x:c r="Q6" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str">
-        <x:v>Python - MCQ - 9.1.6</x:v>
-      </x:c>
-      <x:c r="B7" t="str">
-        <x:v>A profile should remember the name supplied during creation, but `p.name` is missing afterward.
-```python
-class Profile:
-    def __init__(self, name):
-        name = name
-p = Profile('Ira')
-```
-Which replacement correctly stores the name on the object?</x:v>
-      </x:c>
-      <x:c r="C7" t="str">
-        <x:v>`self.name = name` creates or updates the object's `name` attribute. The original assignment only reassigns the local parameter to itself.</x:v>
-      </x:c>
-      <x:c r="D7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E7" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F7" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G7" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H7" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I7" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J7" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K7" t="str">
-        <x:v>constructors</x:v>
-      </x:c>
-      <x:c r="L7"/>
-      <x:c r="M7" t="str">
-        <x:v>`self.name = name`</x:v>
-      </x:c>
-      <x:c r="N7" t="str">
-        <x:v>`name.self = name`</x:v>
-      </x:c>
-      <x:c r="O7" t="str">
-        <x:v>`Profile = name`</x:v>
-      </x:c>
-      <x:c r="P7" t="str">
-        <x:v>`return self`</x:v>
-      </x:c>
-      <x:c r="Q7" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str">
-        <x:v>Python - MCQ - 9.1.7</x:v>
-      </x:c>
-      <x:c r="B8" t="str">
-        <x:v>A parcel class requires both a tracking code and a weight. The app creates one parcel with only the code.
-```python
-class Parcel:
-    def __init__(self, code, weight):
-        self.code = code
-        self.weight = weight
-box = Parcel('PX7')
-print(box.code)
-```
-What happens?</x:v>
-      </x:c>
-      <x:c r="C8" t="str">
-        <x:v>After Python supplies `self`, the constructor still requires values for both `code` and `weight`. Because `weight` is missing, object creation raises `TypeError` before the print statement runs.</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F8" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G8" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H8" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I8" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J8" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K8" t="str">
-        <x:v>constructors</x:v>
-      </x:c>
-      <x:c r="L8"/>
-      <x:c r="M8" t="str">
-        <x:v>It prints `PX7` and gives weight the value 0</x:v>
-      </x:c>
-      <x:c r="N8" t="str">
-        <x:v>It creates the parcel but omits only `weight`</x:v>
-      </x:c>
-      <x:c r="O8" t="str">
-        <x:v>It raises AttributeError at the print statement</x:v>
-      </x:c>
-      <x:c r="P8" t="str">
-        <x:v>It raises TypeError while trying to create the parcel</x:v>
-      </x:c>
-      <x:c r="Q8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str">
-        <x:v>Python - MCQ - 9.1.8</x:v>
-      </x:c>
-      <x:c r="B9" t="str">
-        <x:v>A task object uses one method inside another.
-```python
-class Task:
-    def is_done(self):
-        return self.progress == 100
-    def label(self):
-        return 'Done' if self.is_done() else 'Open'
-t = Task()
-t.progress = 100
-print(t.label())
-```
-What is displayed?</x:v>
-      </x:c>
-      <x:c r="C9" t="str">
-        <x:v>`label` calls `is_done` on the same object through `self`. Since the object's progress is 100, `is_done` returns `True` and `label` returns `Done`.</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E9" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F9" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G9" t="str">
+    ______
+```</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>`pass` is a valid placeholder statement in a class body and adds no data or behaviour.</x:v>
+      </x:c>
+      <x:c r="D10" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
         <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H9" t="str">
-        <x:v>python - Set 1</x:v>
-      </x:c>
-      <x:c r="I9" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J9" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K9" t="str">
-        <x:v>attributes-and-methods</x:v>
-      </x:c>
-      <x:c r="L9"/>
-      <x:c r="M9" t="str">
-        <x:v>Open</x:v>
-      </x:c>
-      <x:c r="N9" t="str">
-        <x:v>True</x:v>
-      </x:c>
-      <x:c r="O9" t="str">
-        <x:v>Done</x:v>
-      </x:c>
-      <x:c r="P9" t="str">
-        <x:v>The progress value 100</x:v>
-      </x:c>
-      <x:c r="Q9" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="str">
-        <x:v>Python - MCQ - 9.1.9</x:v>
-      </x:c>
-      <x:c r="B10" t="str">
-        <x:v>A prepaid card rejects withdrawals larger than its balance.
-```python
-class Card:
-    def __init__(self, balance):
-        self.balance = balance
-    def add(self, amount):
-        self.balance += amount
-    def spend(self, amount):
-        if amount &lt;= self.balance:
-            self.balance -= amount
-card = Card(80)
-card.spend(30)
-card.add(25)
-card.spend(90)
-print(card.balance)
-```
-What final balance is displayed?</x:v>
-      </x:c>
-      <x:c r="C10" t="str">
-        <x:v>The first purchase changes 80 to 50, and adding 25 changes it to 75. The attempted purchase of 90 is rejected, so the stored balance remains 75.</x:v>
-      </x:c>
-      <x:c r="D10" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E10" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F10" t="str">
-        <x:v>hard</x:v>
-      </x:c>
-      <x:c r="G10" t="str">
-        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H10" t="str">
         <x:v>python - Set 1</x:v>
@@ -912,34 +901,44 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K10" t="str">
-        <x:v>modeling-with-classes</x:v>
+        <x:v>classes-and-objects</x:v>
       </x:c>
       <x:c r="L10"/>
       <x:c r="M10" t="str">
-        <x:v>-15</x:v>
+        <x:v>`Sensor = None`</x:v>
       </x:c>
       <x:c r="N10" t="str">
-        <x:v>75</x:v>
+        <x:v>`pass`</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>90</x:v>
+        <x:v>`def read(self): return None`</x:v>
       </x:c>
       <x:c r="P10" t="str">
-        <x:v>165</x:v>
+        <x:v>`status = "unknown"`</x:v>
       </x:c>
       <x:c r="Q10" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="198" hidden="0" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>Python - MCQ - 9.1.10</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>A library currently stores each book as a dictionary. The next version must let every book calculate its overdue fee using the same rule. Which design best fits the new requirement?</x:v>
+        <x:v>A default constructor value is overridden once
+A dashboard creates two counters:
+```python
+class Counter:
+    def __init__(self, value=0):
+        self.value = value
+left = Counter()
+right = Counter(5)
+left.value += 2
+```
+Which state is present after the final assignment?</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>A class is useful when each entity has related data and shared behavior. A `Book` class can store the title and days overdue while its method applies the fee rule consistently.</x:v>
+        <x:v>The omitted argument gives `left` zero before its increment to two, while `right` keeps its explicitly supplied value of five.</x:v>
       </x:c>
       <x:c r="D11" t="n">
         <x:v>1</x:v>
@@ -951,7 +950,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G11" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H11" t="str">
         <x:v>python - Set 1</x:v>
@@ -963,34 +962,42 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>modeling-with-classes</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L11"/>
       <x:c r="M11" t="str">
-        <x:v>Use a Book class with attributes and an overdue-fee method</x:v>
+        <x:v>`left.value == 0` and `right.value == 7`</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>Keep unrelated variables for every book and repeat the formula</x:v>
+        <x:v>`left.value == 7` and `right.value == 7`</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Store only the titles because methods cannot use numbers</x:v>
+        <x:v>`left.value == 5` and `right.value == 2`</x:v>
       </x:c>
       <x:c r="P11" t="str">
-        <x:v>Put all book details into one long string</x:v>
+        <x:v>`left.value == 2` and `right.value == 5`</x:v>
       </x:c>
       <x:c r="Q11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>Python - MCQ - 9.2.1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>A developer wants to define an empty `Badge` class now and add attributes to its objects later. Why is `pass` placed in the class body?</x:v>
+        <x:v>Two calls use the same empty class
+```python
+class PassCard:
+    pass
+card_a = PassCard()
+card_b = PassCard()
+same = card_a is card_b
+```
+Which value is assigned to `same`?</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Python requires an indented class body. `pass` is a placeholder that performs no action, allowing an intentionally empty class definition to be valid.</x:v>
+        <x:v>Each class call creates a new object, so identity comparison with `is` returns `False`.</x:v>
       </x:c>
       <x:c r="D12" t="n">
         <x:v>1</x:v>
@@ -999,10 +1006,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F12" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G12" t="str">
-        <x:v>understand</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H12" t="str">
         <x:v>python - Set 2</x:v>
@@ -1018,30 +1025,31 @@
       </x:c>
       <x:c r="L12"/>
       <x:c r="M12" t="str">
-        <x:v>It creates one Badge object automatically</x:v>
+        <x:v>`False`, because the two calls create distinct objects</x:v>
       </x:c>
       <x:c r="N12" t="str">
-        <x:v>It prevents attributes from being added later</x:v>
+        <x:v>`True`, because both objects have no attributes</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>It supplies a valid empty class body</x:v>
+        <x:v>`None`, because `is` works only with numbers and strings</x:v>
       </x:c>
       <x:c r="P12" t="str">
-        <x:v>It makes every object compare as equal</x:v>
+        <x:v>The comparison fails because empty classes cannot be instantiated twice</x:v>
       </x:c>
       <x:c r="Q12" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>Python - MCQ - 9.2.2</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>A student is creating a class for course records. Which line correctly begins the class definition using the naming style shown in the unit?</x:v>
+        <x:v>A valid declaration fails the team's class-name check
+A valid declaration, `class bank_account:`, runs successfully but fails the project's class-naming check. The public name should remain the two words "bank account." Which header is the smallest convention-compliant repair?</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>A class definition begins with `class`, uses a capitalized class name by convention, and ends the header with a colon. `class CourseRecord:` satisfies all three.</x:v>
+        <x:v>Python class names conventionally use CapitalisedWords, represented here by `BankAccount`.</x:v>
       </x:c>
       <x:c r="D13" t="n">
         <x:v>1</x:v>
@@ -1050,10 +1058,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F13" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G13" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H13" t="str">
         <x:v>python - Set 2</x:v>
@@ -1069,41 +1077,39 @@
       </x:c>
       <x:c r="L13"/>
       <x:c r="M13" t="str">
-        <x:v>`def CourseRecord:`</x:v>
+        <x:v>`class Bank_Account:`</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>`class courseRecord()`</x:v>
+        <x:v>`class BANKAccount:`</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>`CourseRecord = class`</x:v>
+        <x:v>`class BankAccount:`</x:v>
       </x:c>
       <x:c r="P13" t="str">
-        <x:v>`class CourseRecord:`</x:v>
+        <x:v>`class bankAccount:`</x:v>
       </x:c>
       <x:c r="Q13" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>Python - MCQ - 9.2.3</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Two lamps are separate objects. Only the first lamp is switched on.
+        <x:v>An alias is confused with a fresh instance
 ```python
-class Lamp:
+class Student:
     pass
-left = Lamp()
-right = Lamp()
-left.state = 'on'
-right.state = 'off'
-left.state = 'off'
-print(right.state)
+first = Student()
+second = first
+third = Student()
+first.name = "Asha"
 ```
-What is printed?</x:v>
+Which observation correctly distinguishes assignment from instantiation?</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Each instance stores its own attributes. Changing `left.state` does not change the independent `right` object, whose state remains `off`.</x:v>
+        <x:v>`second = first` creates an alias to the same object, while `third = Student()` creates a new object with no `name`.</x:v>
       </x:c>
       <x:c r="D14" t="n">
         <x:v>1</x:v>
@@ -1112,10 +1118,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F14" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G14" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H14" t="str">
         <x:v>python - Set 2</x:v>
@@ -1127,34 +1133,35 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K14" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>classes-and-objects</x:v>
       </x:c>
       <x:c r="L14"/>
       <x:c r="M14" t="str">
-        <x:v>off</x:v>
+        <x:v>`second.name` is `"Asha"`, while reading `third.name` raises `AttributeError`</x:v>
       </x:c>
       <x:c r="N14" t="str">
-        <x:v>on</x:v>
+        <x:v>Both `second.name` and `third.name` are automatically `"Asha"`</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>None</x:v>
+        <x:v>Reading either name raises `AttributeError` because attributes cannot be added later</x:v>
       </x:c>
       <x:c r="P14" t="str">
-        <x:v>An AttributeError</x:v>
+        <x:v>`third.name` is `"Asha"`, while `second` remains without a name</x:v>
       </x:c>
       <x:c r="Q14" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
+    <x:row r="15" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>Python - MCQ - 9.2.4</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>A bare `Movie` object has just been created from an empty class. Which statement adds the title `Arrival` to that specific object?</x:v>
+        <x:v>Attaching data to one existing object
+An empty `Student` object is stored in `asha`. Which statement attaches roll number 101 to that particular object?</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Dot notation assigns an attribute to an object. `movie.title = 'Arrival'` creates `title` on the object referenced by `movie`.</x:v>
+        <x:v>Dot assignment creates `roll_number` on the specific object referenced by `asha`; the alternatives modify another namespace or replace the reference.</x:v>
       </x:c>
       <x:c r="D15" t="n">
         <x:v>1</x:v>
@@ -1166,7 +1173,7 @@
         <x:v>easy</x:v>
       </x:c>
       <x:c r="G15" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H15" t="str">
         <x:v>python - Set 2</x:v>
@@ -1182,41 +1189,36 @@
       </x:c>
       <x:c r="L15"/>
       <x:c r="M15" t="str">
-        <x:v>`Movie(title) = 'Arrival'`</x:v>
+        <x:v>`Student.roll_number = 101`</x:v>
       </x:c>
       <x:c r="N15" t="str">
-        <x:v>`movie.title = 'Arrival'`</x:v>
+        <x:v>`roll_number = 101`</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>`title.movie = 'Arrival'`</x:v>
+        <x:v>`asha.roll_number = 101`</x:v>
       </x:c>
       <x:c r="P15" t="str">
-        <x:v>`movie = title.Arrival`</x:v>
+        <x:v>`asha = 101`</x:v>
       </x:c>
       <x:c r="Q15" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>Python - MCQ - 9.2.5</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>A counter object updates its stored value whenever `increase` is called.
+        <x:v>Updating one account without disturbing another
 ```python
-class Counter:
-    def increase(self, amount):
-        self.value += amount
-c = Counter()
-c.value = 4
-c.increase(3)
-c.increase(2)
-print(c.value)
+acc1.balance = 1000
+acc2.balance = 1000
+acc1.balance = acc1.balance - 250
 ```
-What value is displayed?</x:v>
+Which pair of balances remains after the update?</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>The method changes the same object's `value` attribute. The two calls update 4 to 7 and then 7 to 9.</x:v>
+        <x:v>Reassigning `acc1.balance` changes that object only; `acc2` retains its separate value.</x:v>
       </x:c>
       <x:c r="D16" t="n">
         <x:v>1</x:v>
@@ -1244,30 +1246,38 @@
       </x:c>
       <x:c r="L16"/>
       <x:c r="M16" t="str">
-        <x:v>The starting value, 4</x:v>
+        <x:v>`acc1` has 750 and `acc2` has 750</x:v>
       </x:c>
       <x:c r="N16" t="str">
-        <x:v>The combined increase, 5</x:v>
+        <x:v>`acc1` has 750 and `acc2` has 1000</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>7 after only the first call</x:v>
+        <x:v>`acc1` has 1000 and `acc2` has 750</x:v>
       </x:c>
       <x:c r="P16" t="str">
-        <x:v>9</x:v>
+        <x:v>Both balances become undefined after reassignment</x:v>
       </x:c>
       <x:c r="Q16" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>Python - MCQ - 9.2.6</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>A developer calls `report.show()` where `show` is defined as `def show(self):`. Which value is received by `self` during that call?</x:v>
+        <x:v>A partially prepared object reaches a report
+```python
+class Student:
+    pass
+meera = Student()
+meera.roll_number = 103
+print(meera.name)
+```
+Which incident classification matches the last line?</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>For an instance-method call, Python automatically passes the object before the dot. Here, `self` refers to the same object as `report`.</x:v>
+        <x:v>Dot lookup raises `AttributeError` when the requested attribute was never attached to that object.</x:v>
       </x:c>
       <x:c r="D17" t="n">
         <x:v>1</x:v>
@@ -1276,10 +1286,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F17" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G17" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H17" t="str">
         <x:v>python - Set 2</x:v>
@@ -1295,39 +1305,31 @@
       </x:c>
       <x:c r="L17"/>
       <x:c r="M17" t="str">
-        <x:v>The text returned by `show`</x:v>
+        <x:v>`KeyError`, because `name` was not used as a dictionary key</x:v>
       </x:c>
       <x:c r="N17" t="str">
-        <x:v>The class name as a string</x:v>
+        <x:v>It displays an empty string because Python automatically supplies defaults for every missing object attribute</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>The object referenced by `report`</x:v>
+        <x:v>`NameError`, because `meera` stops existing after assignment</x:v>
       </x:c>
       <x:c r="P17" t="str">
-        <x:v>No value because `self` is optional</x:v>
+        <x:v>`AttributeError`, because this object was never given a `name` attribute</x:v>
       </x:c>
       <x:c r="Q17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>Python - MCQ - 9.2.7</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>A temperature object converts its stored Celsius value.
-```python
-class Temperature:
-    def fahrenheit(self):
-        return self.celsius * 9 / 5 + 32
-t = Temperature()
-t.celsius = 20
-print(t.fahrenheit())
-```
-What is printed?</x:v>
+        <x:v>Replacing an existing attribute value
+An object begins with `ticket.status = "Open"`. After the issue is resolved, which statement changes only that object's existing status?</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>The method reads `self.celsius`, which is 20. Applying the conversion gives `20 * 9 / 5 + 32`, so Python prints `68.0`.</x:v>
+        <x:v>Assigning through `ticket.status` replaces that object's value; a class attribute, standalone variable, or replaced reference does not perform the requested update.</x:v>
       </x:c>
       <x:c r="D18" t="n">
         <x:v>1</x:v>
@@ -1355,39 +1357,31 @@
       </x:c>
       <x:c r="L18"/>
       <x:c r="M18" t="str">
-        <x:v>20</x:v>
+        <x:v>`Ticket.status = "Closed"`</x:v>
       </x:c>
       <x:c r="N18" t="str">
-        <x:v>68.0</x:v>
+        <x:v>`ticket.status = "Closed"`</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>52.0</x:v>
+        <x:v>`status = "Closed"`</x:v>
       </x:c>
       <x:c r="P18" t="str">
-        <x:v>An AttributeError</x:v>
+        <x:v>`ticket = "Closed"`</x:v>
       </x:c>
       <x:c r="Q18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="19">
+    <x:row r="19" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>Python - MCQ - 9.2.8</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>A label method expects every item to have a `price`, but the setup code assigns only `cost`.
-```python
-class Item:
-    def label(self):
-        return f'₹{self.price}'
-x = Item()
-x.cost = 250
-print(x.label())
-```
-Which diagnosis is correct?</x:v>
+        <x:v>Preventing incomplete objects rather than detecting them later
+A program creates fifty student objects and then manually assigns `name`, `roll_number`, and `marks` in three separate lines for each one. Missing one line causes a delayed `AttributeError`. Which structural repair addresses the source of the defect?</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>The method looks for `self.price`, but the object has only `cost`. The mismatched attribute name causes `AttributeError` when `label` runs.</x:v>
+        <x:v>A constructor makes the required setup part of creation, preventing partially prepared objects.</x:v>
       </x:c>
       <x:c r="D19" t="n">
         <x:v>1</x:v>
@@ -1396,10 +1390,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F19" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G19" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H19" t="str">
         <x:v>python - Set 2</x:v>
@@ -1411,225 +1405,212 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L19"/>
       <x:c r="M19" t="str">
-        <x:v>`label` raises AttributeError because `price` was never assigned</x:v>
+        <x:v>Require those values in `__init__` and assign them to `self` during creation</x:v>
       </x:c>
       <x:c r="N19" t="str">
-        <x:v>The code prints ₹250 because `cost` and `price` are synonyms</x:v>
+        <x:v>Catch every later `AttributeError` and continue with a blank report</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>The code prints ₹0 because missing numbers default to zero</x:v>
+        <x:v>Add a fourth parallel list recording which assignments were forgotten</x:v>
       </x:c>
       <x:c r="P19" t="str">
-        <x:v>Creating `x` fails because the class has no constructor</x:v>
+        <x:v>Sort the objects before reading their attributes</x:v>
       </x:c>
       <x:c r="Q19" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="20">
+    <x:row r="20" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>Python - MCQ - 9.2.9</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>A points method updates an account and returns the new total.
+        <x:v>Placing behaviour on the blueprint
+A `Student` object should answer whether its own marks meet the pass boundary. Which class member has the correct basic method shape?</x:v>
+      </x:c>
+      <x:c r="C20" t="str">
+        <x:v>The correct method receives the object as `self`, reads its attribute, and explicitly returns the Boolean result.</x:v>
+      </x:c>
+      <x:c r="D20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E20" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F20" t="str">
+        <x:v>easy</x:v>
+      </x:c>
+      <x:c r="G20" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H20" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I20" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J20" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K20" t="str">
+        <x:v>attributes-and-methods</x:v>
+      </x:c>
+      <x:c r="L20"/>
+      <x:c r="M20" t="str">
+        <x:v>`def has_passed(marks): return marks &gt;= 40`</x:v>
+      </x:c>
+      <x:c r="N20" t="str">
+        <x:v>`def has_passed(self): return marks &gt;= 40`</x:v>
+      </x:c>
+      <x:c r="O20" t="str">
+        <x:v>`def has_passed(self): result = self.marks &gt;= 40`</x:v>
+      </x:c>
+      <x:c r="P20" t="str">
+        <x:v>`def has_passed(self): return self.marks &gt;= 40`</x:v>
+      </x:c>
+      <x:c r="Q20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A21" t="str">
+        <x:v>Python - MCQ - 9.2.10</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>The same method serves different objects
+```python
+class Student:
+    def result(self):
+        return self.marks &gt;= 40
+asha.marks = 78
+ravi.marks = 32
+```
+Which pair follows from `asha.result()` and `ravi.result()`?</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>In each call, `self` refers to the object before the dot, so the two marks produce different Boolean results.</x:v>
+      </x:c>
+      <x:c r="D21" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>python - Set 2</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>attributes-and-methods</x:v>
+      </x:c>
+      <x:c r="L21"/>
+      <x:c r="M21" t="str">
+        <x:v>Both calls return `True` because the method is shared</x:v>
+      </x:c>
+      <x:c r="N21" t="str">
+        <x:v>Both calls return `False` because `marks` is outside the method</x:v>
+      </x:c>
+      <x:c r="O21" t="str">
+        <x:v>The calls return `True` and `False`, using each calling object's marks</x:v>
+      </x:c>
+      <x:c r="P21" t="str">
+        <x:v>The first call permanently changes the shared method, forcing the second call to use Asha's marks</x:v>
+      </x:c>
+      <x:c r="Q21" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A22" t="str">
+        <x:v>Python - MCQ - 9.3.1</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>A method definition leaves no place for the object argument
+```python
+class Greeter:
+    def welcome():
+        return "Welcome"
+guest = Greeter()
+message = guest.welcome()
+```
+Which explanation matches the failed call?</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>An object method call automatically passes the object, causing a `TypeError` when no first parameter exists.</x:v>
+      </x:c>
+      <x:c r="D22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>published</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>apply</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>python - Set 3</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>python</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>object-oriented-programming-intro</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>attributes-and-methods</x:v>
+      </x:c>
+      <x:c r="L22"/>
+      <x:c r="M22" t="str">
+        <x:v>Python supplies `guest` automatically, but `welcome` has no parameter to receive it</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>Methods are required to print a message rather than return one</x:v>
+      </x:c>
+      <x:c r="O22" t="str">
+        <x:v>The class must contain an attribute before it may contain a method</x:v>
+      </x:c>
+      <x:c r="P22" t="str">
+        <x:v>`welcome` can only be called by writing `Greeter.welcome()` because methods never receive an object automatically</x:v>
+      </x:c>
+      <x:c r="Q22" t="n">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="158.39999389648438" hidden="0" customHeight="1">
+      <x:c r="A23" t="str">
+        <x:v>Python - MCQ - 9.3.2</x:v>
+      </x:c>
+      <x:c r="B23" t="str">
+        <x:v>Supplying a method's ordinary argument
 ```python
 class Account:
-    def add_points(self, points):
-        self.points += points
-        return self.points
-a = Account()
-a.points = 10
-print(a.add_points(5), a.points)
+    def can_withdraw(self, amount):
+        return amount &lt;= self.balance
+acc.balance = 500
+allowed = acc.can_withdraw(450)
 ```
-What is displayed?</x:v>
-      </x:c>
-      <x:c r="C20" t="str">
-        <x:v>The method changes `a.points` from 10 to 15 and returns that same new value. Both expressions supplied to `print` therefore evaluate to 15.</x:v>
-      </x:c>
-      <x:c r="D20" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E20" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F20" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G20" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H20" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I20" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J20" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K20" t="str">
-        <x:v>attributes-and-methods</x:v>
-      </x:c>
-      <x:c r="L20"/>
-      <x:c r="M20" t="str">
-        <x:v>10 15</x:v>
-      </x:c>
-      <x:c r="N20" t="str">
-        <x:v>15 10</x:v>
-      </x:c>
-      <x:c r="O20" t="str">
-        <x:v>15 15</x:v>
-      </x:c>
-      <x:c r="P20" t="str">
-        <x:v>5 15</x:v>
-      </x:c>
-      <x:c r="Q20" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="str">
-        <x:v>Python - MCQ - 9.2.10</x:v>
-      </x:c>
-      <x:c r="B21" t="str">
-        <x:v>A booking object is given a second name instead of creating a new booking.
-```python
-class Booking:
-    pass
-first = Booking()
-first.status = 'open'
-second = first
-second.status = 'closed'
-print(first.status)
-```
-What is printed?</x:v>
-      </x:c>
-      <x:c r="C21" t="str">
-        <x:v>`second = first` makes both variables refer to the same object. Updating the object through `second` is therefore visible through `first`.</x:v>
-      </x:c>
-      <x:c r="D21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E21" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F21" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G21" t="str">
-        <x:v>analyze</x:v>
-      </x:c>
-      <x:c r="H21" t="str">
-        <x:v>python - Set 2</x:v>
-      </x:c>
-      <x:c r="I21" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J21" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K21" t="str">
-        <x:v>classes-and-objects</x:v>
-      </x:c>
-      <x:c r="L21"/>
-      <x:c r="M21" t="str">
-        <x:v>open</x:v>
-      </x:c>
-      <x:c r="N21" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="O21" t="str">
-        <x:v>An AttributeError</x:v>
-      </x:c>
-      <x:c r="P21" t="str">
-        <x:v>closed</x:v>
-      </x:c>
-      <x:c r="Q21" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="str">
-        <x:v>Python - MCQ - 9.3.1</x:v>
-      </x:c>
-      <x:c r="B22" t="str">
-        <x:v>A notification class gives new messages a default priority.
-```python
-class Notice:
-    def __init__(self, text, priority='normal'):
-        self.text = text
-        self.priority = priority
-n = Notice('Server ready')
-print(n.priority)
-```
-What is displayed?</x:v>
-      </x:c>
-      <x:c r="C22" t="str">
-        <x:v>The call supplies no priority, so the constructor uses its default value, `normal`, and stores it on the object.</x:v>
-      </x:c>
-      <x:c r="D22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E22" t="str">
-        <x:v>published</x:v>
-      </x:c>
-      <x:c r="F22" t="str">
-        <x:v>medium</x:v>
-      </x:c>
-      <x:c r="G22" t="str">
-        <x:v>apply</x:v>
-      </x:c>
-      <x:c r="H22" t="str">
-        <x:v>python - Set 3</x:v>
-      </x:c>
-      <x:c r="I22" t="str">
-        <x:v>python</x:v>
-      </x:c>
-      <x:c r="J22" t="str">
-        <x:v>object-oriented-programming-intro</x:v>
-      </x:c>
-      <x:c r="K22" t="str">
-        <x:v>constructors</x:v>
-      </x:c>
-      <x:c r="L22"/>
-      <x:c r="M22" t="str">
-        <x:v>normal</x:v>
-      </x:c>
-      <x:c r="N22" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="O22" t="str">
-        <x:v>Server ready</x:v>
-      </x:c>
-      <x:c r="P22" t="str">
-        <x:v>A TypeError</x:v>
-      </x:c>
-      <x:c r="Q22" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="str">
-        <x:v>Python - MCQ - 9.3.2</x:v>
-      </x:c>
-      <x:c r="B23" t="str">
-        <x:v>A ticket constructor accepts `zone` first and `seat` second.
-```python
-class Ticket:
-    def __init__(self, zone, seat):
-        self.zone = zone
-        self.seat = seat
-t = Ticket('B', 14)
-print(t.seat, t.zone)
-```
-What does the final line display?</x:v>
+How are the two parameters supplied during the call?</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Positional arguments are matched in order: `zone` receives `B` and `seat` receives 14. The print statement requests the seat before the zone.</x:v>
+        <x:v>Python supplies the calling object as `self`; the explicitly supplied 450 fills `amount`.</x:v>
       </x:c>
       <x:c r="D23" t="n">
         <x:v>1</x:v>
@@ -1641,7 +1622,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G23" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H23" t="str">
         <x:v>python - Set 3</x:v>
@@ -1653,43 +1634,42 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>constructors</x:v>
+        <x:v>attributes-and-methods</x:v>
       </x:c>
       <x:c r="L23"/>
       <x:c r="M23" t="str">
-        <x:v>B 14</x:v>
+        <x:v>`450` becomes `self`, and `amount` remains missing</x:v>
       </x:c>
       <x:c r="N23" t="str">
-        <x:v>zone seat</x:v>
+        <x:v>Both `self` and `amount` receive the value `450`</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>14 B</x:v>
+        <x:v>The caller must pass `acc` again after `450`, because Python supplies neither method parameter automatically</x:v>
       </x:c>
       <x:c r="P23" t="str">
-        <x:v>14 zone</x:v>
+        <x:v>Python supplies `acc` as `self`, and `450` becomes `amount`</x:v>
       </x:c>
       <x:c r="Q23" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>Python - MCQ - 9.3.3</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>A room object is created with keyword arguments in a different order from the constructor parameters.
+        <x:v>One method reuses another method's decision
 ```python
-class Room:
-    def __init__(self, floor, number):
-        self.floor = floor
-        self.number = number
-r = Room(number=204, floor=2)
-print(r.floor, r.number)
+class Student:
+    def has_passed(self):
+        return self.marks &gt;= 40
+    def report(self):
+        return "Pass" if self.has_passed() else "Fail"
 ```
-What is displayed?</x:v>
+Which detail makes `report` evaluate the same student's marks?</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Keyword arguments are matched by parameter name, not by their written order. The object stores floor 2 and room number 204.</x:v>
+        <x:v>Calling through `self` keeps the delegated method on the current student object.</x:v>
       </x:c>
       <x:c r="D24" t="n">
         <x:v>1</x:v>
@@ -1713,44 +1693,40 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>constructors</x:v>
+        <x:v>attributes-and-methods</x:v>
       </x:c>
       <x:c r="L24"/>
       <x:c r="M24" t="str">
-        <x:v>204 2</x:v>
+        <x:v>`has_passed` becomes a global function when `report` begins</x:v>
       </x:c>
       <x:c r="N24" t="str">
-        <x:v>2 204</x:v>
+        <x:v>Python copies `marks` into every local variable named `self`</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>number floor</x:v>
+        <x:v>`self.has_passed()` calls the method on the current object</x:v>
       </x:c>
       <x:c r="P24" t="str">
-        <x:v>A TypeError</x:v>
+        <x:v>The conditional expression ignores the result of `has_passed`</x:v>
       </x:c>
       <x:c r="Q24" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>Python - MCQ - 9.3.4</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>An employee constructor appears to receive a department, but the object cannot report it.
+        <x:v>A rename method updates a temporary name
 ```python
-class Employee:
-    def __init__(self, department):
-        department = department.upper()
-    def label(self):
-        return self.department
-e = Employee('sales')
-print(e.label())
+class Student:
+    def rename(self, new_name):
+        name = new_name
 ```
-Which change fixes the root cause?</x:v>
+Calling `asha.rename("Asha Rao")` leaves `asha.name` unchanged. Which smallest repair makes the method update the object's attribute?</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>The constructor currently changes only its local parameter. Assigning the transformed value to `self.department` stores it on the object for `label` to read.</x:v>
+        <x:v>The original assignment creates a local variable; dot assignment is needed to replace the instance attribute.</x:v>
       </x:c>
       <x:c r="D25" t="n">
         <x:v>1</x:v>
@@ -1762,7 +1738,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G25" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H25" t="str">
         <x:v>python - Set 3</x:v>
@@ -1774,34 +1750,41 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>constructors</x:v>
+        <x:v>attributes-and-methods</x:v>
       </x:c>
       <x:c r="L25"/>
       <x:c r="M25" t="str">
-        <x:v>Replace `return` with `print` in `label`</x:v>
+        <x:v>Replace the body with `new_name = name`</x:v>
       </x:c>
       <x:c r="N25" t="str">
-        <x:v>Call `Employee.label()` without an object</x:v>
+        <x:v>Replace the body with `self.name = new_name`</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Add `pass` after the constructor</x:v>
+        <x:v>Call the method as `asha.rename(self, "Asha Rao")`</x:v>
       </x:c>
       <x:c r="P25" t="str">
-        <x:v>Use `self.department = department.upper()` in `__init__`</x:v>
+        <x:v>Move `name = new_name` outside the class</x:v>
       </x:c>
       <x:c r="Q25" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>Python - MCQ - 9.3.5</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>A product method is intended to reduce its stored stock. Which method body correctly changes the object's attribute rather than only a temporary local value?</x:v>
+        <x:v>Setup occurs without a separate method call
+```python
+class Device:
+    def __init__(self):
+        self.status = "offline"
+router = Device()
+```
+Which statement describes the state immediately after the last line?</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>`self.stock -= amount` reads and updates the `stock` attribute on the current object. Assignments to a separate local name do not change the object's state.</x:v>
+        <x:v>Python invokes `__init__` during `Device()`, so the new object starts with the assigned status.</x:v>
       </x:c>
       <x:c r="D26" t="n">
         <x:v>1</x:v>
@@ -1810,7 +1793,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F26" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G26" t="str">
         <x:v>analyze</x:v>
@@ -1825,47 +1808,42 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L26"/>
       <x:c r="M26" t="str">
-        <x:v>`stock = stock - amount`</x:v>
+        <x:v>`router.status` is missing until `router.__init__()` is called manually</x:v>
       </x:c>
       <x:c r="N26" t="str">
-        <x:v>`amount = self.stock`</x:v>
+        <x:v>The class stores `"offline"`, but the object does not</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>`self.stock -= amount`</x:v>
+        <x:v>`router.status` is `"offline"` because `__init__` ran automatically</x:v>
       </x:c>
       <x:c r="P26" t="str">
-        <x:v>`return stock.amount`</x:v>
+        <x:v>`router` contains only a method and cannot hold data</x:v>
       </x:c>
       <x:c r="Q26" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
-    <x:row r="27">
+    <x:row r="27" ht="158.39999389648438" hidden="0" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>Python - MCQ - 9.3.6</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>A grading app classifies scores using its stored value.
+        <x:v>Constructor arguments are stored on the correct instance
 ```python
-class Result:
-    def __init__(self, score):
-        self.score = score
-    def grade(self):
-        if self.score &gt;= 90:
-            return 'A'
-        if self.score &gt;= 75:
-            return 'B'
-        return 'C'
-print(Result(75).grade())
+class Student:
+    def __init__(self, name, marks):
+        self.name = name
+        self.marks = marks
+learner = Student("Kabir", 84)
 ```
-Which grade is printed?</x:v>
+Which state belongs to `learner`?</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>The score does not meet the 90 threshold, but it does meet the inclusive 75 threshold. The method therefore returns `B`.</x:v>
+        <x:v>Constructor arguments bind by position and are stored by the two `self.attribute` assignments.</x:v>
       </x:c>
       <x:c r="D27" t="n">
         <x:v>1</x:v>
@@ -1889,45 +1867,43 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>modeling-with-classes</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L27"/>
       <x:c r="M27" t="str">
-        <x:v>B</x:v>
+        <x:v>`name` is 84 and `marks` is `"Kabir"`</x:v>
       </x:c>
       <x:c r="N27" t="str">
-        <x:v>A</x:v>
+        <x:v>`name` is `"Kabir"` and `marks` is 84</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>C</x:v>
+        <x:v>Both attributes contain the complete argument tuple</x:v>
       </x:c>
       <x:c r="P27" t="str">
-        <x:v>No grade</x:v>
+        <x:v>The arguments disappear because the constructor returns nothing</x:v>
       </x:c>
       <x:c r="Q27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="171.60000610351562" hidden="0" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>Python - MCQ - 9.3.7</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>A task board creates two task objects and asks each for its status.
+        <x:v>Creation is blocked when required data is absent
 ```python
-class Task:
-    def __init__(self, name, done):
+class Student:
+    def __init__(self, name, roll_number, marks):
         self.name = name
-        self.done = done
-    def status(self):
-        return self.name + ':' + ('done' if self.done else 'open')
-tasks = [Task('Test', True), Task('Deploy', False)]
-print(tasks[0].status(), tasks[1].status())
+        self.roll_number = roll_number
+        self.marks = marks
+record = Student("Leela", 108)
 ```
-What is displayed?</x:v>
+Which result protects the program from receiving an incomplete object?</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Each method call reads the state of its own object. The first task is done and the second is open, so both labels reflect their separate values.</x:v>
+        <x:v>Omitting the required `marks` argument raises `TypeError` during construction instead of creating an incomplete object.</x:v>
       </x:c>
       <x:c r="D28" t="n">
         <x:v>1</x:v>
@@ -1951,51 +1927,41 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>modeling-with-classes</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L28"/>
       <x:c r="M28" t="str">
-        <x:v>Test:open Deploy:done</x:v>
+        <x:v>The object is created with `marks` equal to zero</x:v>
       </x:c>
       <x:c r="N28" t="str">
-        <x:v>done open</x:v>
+        <x:v>Python stores `None` for the missing attribute</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Test Deploy</x:v>
+        <x:v>The constructor skips all assignments and returns an empty object</x:v>
       </x:c>
       <x:c r="P28" t="str">
-        <x:v>Test:done Deploy:open</x:v>
+        <x:v>A `TypeError` reports the missing required `marks` argument</x:v>
       </x:c>
       <x:c r="Q28" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
-    <x:row r="29">
+    <x:row r="29" ht="132" hidden="0" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>Python - MCQ - 9.3.8</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>A wallet ignores any payment larger than the available balance.
+        <x:v>A new account uses the standard opening balance
 ```python
-class Wallet:
-    def __init__(self, balance):
+class Account:
+    def __init__(self, holder, balance=0):
+        self.holder = holder
         self.balance = balance
-    def deposit(self, amount):
-        self.balance += amount
-    def pay(self, amount):
-        if amount &lt;= self.balance:
-            self.balance -= amount
-w = Wallet(100)
-w.pay(35)
-w.deposit(20)
-w.pay(90)
-w.pay(40)
-print(w.balance)
 ```
-What is the final balance?</x:v>
+Which call creates Neha's account with the declared default balance?</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>The balance moves from 100 to 65, then to 85. The payment of 90 is ignored, and the final payment of 40 succeeds, leaving 45.</x:v>
+        <x:v>The holder is supplied and the omitted balance uses its declared default of zero.</x:v>
       </x:c>
       <x:c r="D29" t="n">
         <x:v>1</x:v>
@@ -2004,10 +1970,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F29" t="str">
-        <x:v>hard</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G29" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H29" t="str">
         <x:v>python - Set 3</x:v>
@@ -2019,46 +1985,40 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>modeling-with-classes</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L29"/>
       <x:c r="M29" t="str">
-        <x:v>-45</x:v>
+        <x:v>`neha = Account("Neha")`</x:v>
       </x:c>
       <x:c r="N29" t="str">
-        <x:v>45</x:v>
+        <x:v>`neha = Account(balance="Neha")`</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>85</x:v>
+        <x:v>`neha = Account()`</x:v>
       </x:c>
       <x:c r="P29" t="str">
-        <x:v>125</x:v>
+        <x:v>`neha = Account(0, "Neha")`</x:v>
       </x:c>
       <x:c r="Q29" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="118.80000305175781" hidden="0" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>Python - MCQ - 9.3.9</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>A rectangle method reuses another method on the same object.
+        <x:v>A constructor reads an attribute before creating it
 ```python
-class Rectangle:
-    def area(self):
-        return self.width * self.height
-    def is_large(self):
-        return self.area() &gt;= 20
-r = Rectangle()
-r.width = 4
-r.height = 5
-print(r.is_large())
+class Student:
+    def __init__(self, name):
+        self.name = self.name
 ```
-What is displayed?</x:v>
+Instantiation fails because the right side requests an attribute that does not yet exist. Which minimal repair stores the supplied argument?</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>`is_large` calls `self.area()`, which returns 20. Since 20 meets the inclusive threshold, the comparison returns `True`.</x:v>
+        <x:v>The right side must use the parameter `name`; the left side creates the object's `name` attribute.</x:v>
       </x:c>
       <x:c r="D30" t="n">
         <x:v>1</x:v>
@@ -2067,10 +2027,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F30" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G30" t="str">
-        <x:v>apply</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H30" t="str">
         <x:v>python - Set 3</x:v>
@@ -2082,48 +2042,41 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L30"/>
       <x:c r="M30" t="str">
-        <x:v>20</x:v>
+        <x:v>Change the body to `name = self.name`</x:v>
       </x:c>
       <x:c r="N30" t="str">
-        <x:v>False</x:v>
+        <x:v>Remove the `name` parameter and keep the body</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>True</x:v>
+        <x:v>Change the body to `self = name`</x:v>
       </x:c>
       <x:c r="P30" t="str">
-        <x:v>An AttributeError</x:v>
+        <x:v>Change the body to `self.name = name`</x:v>
       </x:c>
       <x:c r="Q30" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>Python - MCQ - 9.3.10</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>A stock object is updated through two methods.
+        <x:v>A nearly correct special-method name is never recognised
 ```python
-class Stock:
-    def add(self, amount):
-        self.units += amount
-    def sell(self, amount):
-        if amount &lt;= self.units:
-            self.units -= amount
-        return self.units
-s = Stock()
-s.units = 12
-s.add(5)
-print(s.sell(20), s.sell(4))
+class Product:
+    def _init_(self, price):
+        self.price = price
+item = Product(250)
 ```
-What is displayed?</x:v>
+Which repair restores automatic constructor behaviour?</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>After adding 5, the stock is 17. Selling 20 is rejected and returns 17; selling 4 then succeeds and returns 13, so the two printed values differ.</x:v>
+        <x:v>Python recognises the constructor only with the exact special name `__init__`.</x:v>
       </x:c>
       <x:c r="D31" t="n">
         <x:v>1</x:v>
@@ -2135,7 +2088,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G31" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H31" t="str">
         <x:v>python - Set 3</x:v>
@@ -2147,34 +2100,43 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>constructors</x:v>
       </x:c>
       <x:c r="L31"/>
       <x:c r="M31" t="str">
-        <x:v>-3 -7</x:v>
+        <x:v>Rename the class to `_Product_`</x:v>
       </x:c>
       <x:c r="N31" t="str">
-        <x:v>17 17</x:v>
+        <x:v>Call `_init_` manually before creating `item`, then pass the unfinished object into `Product`</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>13 13</x:v>
+        <x:v>Rename `_init_` to `__init__`, using two underscores on each side</x:v>
       </x:c>
       <x:c r="P31" t="str">
-        <x:v>17 13</x:v>
+        <x:v>Replace `self.price` with a global variable</x:v>
       </x:c>
       <x:c r="Q31" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="184.8000030517578" hidden="0" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>Python - MCQ - 9.4.1</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>A school stores student names and grades in separate lists and repeatedly searches matching indexes. Which class design best represents one student record?</x:v>
+        <x:v>The exact pass boundary is tested
+```python
+class Student:
+    def __init__(self, marks):
+        self.marks = marks
+    def has_passed(self):
+        return self.marks &gt;= 40
+student = Student(40)
+```
+Which decision does `student.has_passed()` return?</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>A `Student` object should bundle one student's name and grade. A method such as `passed` can then apply behavior to that object's own grade.</x:v>
+        <x:v>The `&gt;=` operator includes 40 in the passing range.</x:v>
       </x:c>
       <x:c r="D32" t="n">
         <x:v>1</x:v>
@@ -2183,7 +2145,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F32" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G32" t="str">
         <x:v>analyze</x:v>
@@ -2202,30 +2164,31 @@
       </x:c>
       <x:c r="L32"/>
       <x:c r="M32" t="str">
-        <x:v>A Student class with `name`, `grade`, and a `passed` method</x:v>
+        <x:v>`True`, because the boundary includes 40</x:v>
       </x:c>
       <x:c r="N32" t="str">
-        <x:v>One class for all names and a separate class for all grades</x:v>
+        <x:v>`False`, because passing begins at 41</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>A method that keeps the two original lists as global data</x:v>
+        <x:v>`None`, because methods cannot return Boolean values</x:v>
       </x:c>
       <x:c r="P32" t="str">
-        <x:v>A tuple containing every student name but no grades</x:v>
+        <x:v>The comparison fails because marks is an attribute</x:v>
       </x:c>
       <x:c r="Q32" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="33">
+    <x:row r="33" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>Python - MCQ - 9.4.2</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>An app stores a distance and unit together and must convert the distance through a reusable operation. Why is a class more suitable than a plain two-item tuple here?</x:v>
+        <x:v>An accepted deposit is followed by a rejected withdrawal
+An account begins with 500. Its `deposit` method adds 200. Its `withdraw` method changes the balance only when the requested amount does not exceed the current balance. A withdrawal of 800 is then attempted. Which balance remains?</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>A tuple can group values, but a class can give those values meaningful attributes and place the conversion behavior beside them. That makes the model clearer and keeps its rule reusable.</x:v>
+        <x:v>The deposit raises the balance to 700, and the excessive withdrawal leaves it unchanged.</x:v>
       </x:c>
       <x:c r="D33" t="n">
         <x:v>1</x:v>
@@ -2234,10 +2197,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F33" t="str">
-        <x:v>medium</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G33" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H33" t="str">
         <x:v>python - Set 4</x:v>
@@ -2253,37 +2216,31 @@
       </x:c>
       <x:c r="L33"/>
       <x:c r="M33" t="str">
-        <x:v>A tuple cannot contain a number and text together</x:v>
+        <x:v>`-100`</x:v>
       </x:c>
       <x:c r="N33" t="str">
-        <x:v>A class can bundle named data with the conversion behavior</x:v>
+        <x:v>`700`</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>A class guarantees every conversion is mathematically correct</x:v>
+        <x:v>`500`</x:v>
       </x:c>
       <x:c r="P33" t="str">
-        <x:v>A tuple always changes when a function reads it</x:v>
+        <x:v>`1500`</x:v>
       </x:c>
       <x:c r="Q33" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>Python - MCQ - 9.4.3</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>A class prints a setup message inside `__init__`.
-```python
-class Session:
-    def __init__(self):
-        print('started')
-s = Session()
-```
-When is `started` printed?</x:v>
+        <x:v>Transactions stay with the account that receives them
+`primary` and `savings` are separate `BankAccount` objects, each starting at 1000. The program calls `primary.withdraw(300)` and then `savings.deposit(50)`. Which state is consistent with independent objects?</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>Python calls `__init__` automatically as part of creating the `Session` object. No separate call such as `s.__init__()` is needed.</x:v>
+        <x:v>Each method updates only its receiving object, leaving balances of 700 and 1050.</x:v>
       </x:c>
       <x:c r="D34" t="n">
         <x:v>1</x:v>
@@ -2292,10 +2249,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F34" t="str">
-        <x:v>easy</x:v>
+        <x:v>medium</x:v>
       </x:c>
       <x:c r="G34" t="str">
-        <x:v>understand</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H34" t="str">
         <x:v>python - Set 4</x:v>
@@ -2307,43 +2264,35 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K34" t="str">
-        <x:v>constructors</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L34"/>
       <x:c r="M34" t="str">
-        <x:v>Only when `s.__init__()` is called later</x:v>
+        <x:v>Both balances become 750 because they share the class</x:v>
       </x:c>
       <x:c r="N34" t="str">
-        <x:v>When the class definition is read</x:v>
+        <x:v>`primary` becomes 1050 and `savings` becomes 700</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>When an attribute is first assigned</x:v>
+        <x:v>`primary` becomes 700 and `savings` becomes 1050</x:v>
       </x:c>
       <x:c r="P34" t="str">
-        <x:v>During the call to `Session()`</x:v>
+        <x:v>Both balances remain 1000 because methods cannot change attributes</x:v>
       </x:c>
       <x:c r="Q34" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>Python - MCQ - 9.4.4</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>A developer intended `summary` to be a method, but its indentation places it outside the class.
-```python
-class Report:
-    pass
-def summary(self):
-    return 'ready'
-r = Report()
-print(r.summary())
-```
-What is the correct diagnosis?</x:v>
+        <x:v>Two reports agree today but age differently
+A class already provides `has_passed()` and `grade()`. Version A of `report()` calls those methods. Version B repeats their current conditions exactly inside `report()`. Tests over every integer mark from 0 through 100 currently produce identical reports. Which review conclusion is accurate?</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Indentation determines the class body. Because `summary` is defined at top level, `Report` objects do not receive that method, and `r.summary()` raises `AttributeError`.</x:v>
+        <x:v>Matching conditions make the versions equivalent over the stated marks today, but delegation avoids a duplicate rule that can diverge after a policy change.</x:v>
       </x:c>
       <x:c r="D35" t="n">
         <x:v>1</x:v>
@@ -2355,7 +2304,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G35" t="str">
-        <x:v>analyze</x:v>
+        <x:v>apply</x:v>
       </x:c>
       <x:c r="H35" t="str">
         <x:v>python - Set 4</x:v>
@@ -2367,34 +2316,42 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L35"/>
       <x:c r="M35" t="str">
-        <x:v>The code prints ready because nearby functions become methods</x:v>
+        <x:v>Equivalent now; Version A is less likely to drift after a rule change</x:v>
       </x:c>
       <x:c r="N35" t="str">
-        <x:v>Python passes `r` to the top-level function automatically</x:v>
+        <x:v>They cannot be equivalent because one method is not allowed to call another method on the same object</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>`r.summary()` raises AttributeError because `summary` is outside the class</x:v>
+        <x:v>Version B is necessarily safer because copying a rule creates a second independent source of truth</x:v>
       </x:c>
       <x:c r="P35" t="str">
-        <x:v>The class definition fails because `pass` cannot be used alone</x:v>
+        <x:v>Version A evaluates another student's state whenever it calls through `self`</x:v>
       </x:c>
       <x:c r="Q35" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="145.1999969482422" hidden="0" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>Python - MCQ - 9.4.5</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>A contact constructor stores `phone`, but its display method reads `phone_number`. Which repair preserves one consistent attribute name?</x:v>
+        <x:v>Withdrawing the full balance is rejected by one character
+```python
+def withdraw(self, amount):
+    if amount &gt;= self.balance:
+        return "Insufficient"
+    self.balance -= amount
+    return "Accepted"
+```
+The policy allows an account to withdraw exactly its current balance. Which smallest repair implements that boundary correctly?</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>The constructor and method must refer to the same object attribute. Changing the method to read `self.phone` matches the attribute that was actually stored.</x:v>
+        <x:v>Only amounts greater than the balance should be rejected; an equal amount must reach the subtraction.</x:v>
       </x:c>
       <x:c r="D36" t="n">
         <x:v>1</x:v>
@@ -2403,7 +2360,7 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F36" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G36" t="str">
         <x:v>analyze</x:v>
@@ -2418,34 +2375,45 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>attributes-and-methods</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L36"/>
       <x:c r="M36" t="str">
-        <x:v>Remove `self` from both places</x:v>
+        <x:v>Change the condition to `amount &lt; self.balance`</x:v>
       </x:c>
       <x:c r="N36" t="str">
-        <x:v>Change the method to read `self.phone`</x:v>
+        <x:v>Change the condition to `amount &gt; self.balance`</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Replace the constructor with `pass`</x:v>
+        <x:v>Change the subtraction to `self.balance += amount`</x:v>
       </x:c>
       <x:c r="P36" t="str">
-        <x:v>Call the method before creating the object</x:v>
+        <x:v>Remove the condition and accept every request</x:v>
       </x:c>
       <x:c r="Q36" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="198" hidden="0" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>Python - MCQ - 9.4.6</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>A new savings account should start at zero unless a balance is supplied. Which constructor header and assignment implement that rule?</x:v>
+        <x:v>A deposit method changes the wrong account
+```python
+class Account:
+    def deposit(self, amount):
+        main_account.balance += amount
+main_account = Account()
+savings = Account()
+main_account.balance = 100
+savings.balance = 400
+savings.deposit(50)
+```
+The call is intended to update whichever account receives it. Which repair achieves that behaviour?</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>A default parameter lets the caller omit the opening balance. Assigning it to `self.balance` ensures every created account has the attribute.</x:v>
+        <x:v>`self` refers to the object that received the call, so the deposit updates `savings` in this scenario.</x:v>
       </x:c>
       <x:c r="D37" t="n">
         <x:v>1</x:v>
@@ -2454,10 +2422,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F37" t="str">
-        <x:v>medium</x:v>
+        <x:v>hard</x:v>
       </x:c>
       <x:c r="G37" t="str">
-        <x:v>apply</x:v>
+        <x:v>analyze</x:v>
       </x:c>
       <x:c r="H37" t="str">
         <x:v>python - Set 4</x:v>
@@ -2469,45 +2437,35 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>constructors</x:v>
+        <x:v>attributes-and-methods</x:v>
       </x:c>
       <x:c r="L37"/>
       <x:c r="M37" t="str">
-        <x:v>`def __init__(self, balance=0): self.balance = balance`</x:v>
+        <x:v>Replace the body with `amount += main_account.balance`</x:v>
       </x:c>
       <x:c r="N37" t="str">
-        <x:v>`def __init__(balance): balance = 0`</x:v>
+        <x:v>Pass `main_account` manually whenever `savings.deposit` is called</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>`def init(self): return balance`</x:v>
+        <x:v>Move both balances into one global variable shared by the objects</x:v>
       </x:c>
       <x:c r="P37" t="str">
-        <x:v>`def __init__(self): balance.self = 0`</x:v>
+        <x:v>Replace the body with `self.balance += amount`</x:v>
       </x:c>
       <x:c r="Q37" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>Python - MCQ - 9.4.7</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>Two variables refer to one meter object.
-```python
-class Meter:
-    def add(self, value):
-        self.total += value
-m1 = Meter()
-m1.total = 5
-m2 = m1
-m2.add(4)
-print(m1.total, m1 is m2)
-```
-What does the final line display?</x:v>
+        <x:v>A single daily count needs no personal behaviour
+The help desk only needs to store today's visitor count, `47`, and perform ordinary arithmetic with it. Which representation is most appropriate?</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>The assignment does not create a second object; both variables are aliases for the same meter. The method changes its total to 9, and the identity check is `True`.</x:v>
+        <x:v>A standalone number with no attached behaviour needs only a normal variable.</x:v>
       </x:c>
       <x:c r="D38" t="n">
         <x:v>1</x:v>
@@ -2516,10 +2474,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F38" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G38" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H38" t="str">
         <x:v>python - Set 4</x:v>
@@ -2531,49 +2489,35 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>classes-and-objects</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L38"/>
       <x:c r="M38" t="str">
-        <x:v>5 False</x:v>
+        <x:v>A plain numeric variable</x:v>
       </x:c>
       <x:c r="N38" t="str">
-        <x:v>9 False</x:v>
+        <x:v>A `VisitorCount` class with a constructor and four methods</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>9 True</x:v>
+        <x:v>One object per visitor even though no visitor details are stored</x:v>
       </x:c>
       <x:c r="P38" t="str">
-        <x:v>5 True</x:v>
+        <x:v>Two parallel lists containing the same count</x:v>
       </x:c>
       <x:c r="Q38" t="n">
-        <x:v>3</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>Python - MCQ - 9.4.8</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>A bank account rejects withdrawals that exceed the balance and returns whether each attempt succeeded.
-```python
-class Account:
-    def __init__(self, balance):
-        self.balance = balance
-    def withdraw(self, amount):
-        if amount &gt; self.balance:
-            return False
-        self.balance -= amount
-        return True
-a = Account(70)
-first = a.withdraw(80)
-second = a.withdraw(30)
-print(first, second, a.balance)
-```
-What is displayed?</x:v>
+        <x:v>Fixed coordinates carry facts but no actions
+A map marker is represented only by latitude and longitude. The pair has no custom behaviour or rule to enforce. Which structure is a proportionate choice?</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>The first withdrawal is rejected, so it returns `False` and leaves 70. The second succeeds, returns `True`, and reduces the balance to 40.</x:v>
+        <x:v>A tuple is sufficient for a fixed group of related values with no custom behaviour.</x:v>
       </x:c>
       <x:c r="D39" t="n">
         <x:v>1</x:v>
@@ -2582,10 +2526,10 @@
         <x:v>published</x:v>
       </x:c>
       <x:c r="F39" t="str">
-        <x:v>hard</x:v>
+        <x:v>easy</x:v>
       </x:c>
       <x:c r="G39" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H39" t="str">
         <x:v>python - Set 4</x:v>
@@ -2601,30 +2545,31 @@
       </x:c>
       <x:c r="L39"/>
       <x:c r="M39" t="str">
-        <x:v>True True -40</x:v>
+        <x:v>A class whose only method returns the same two values</x:v>
       </x:c>
       <x:c r="N39" t="str">
-        <x:v>False False 70</x:v>
+        <x:v>A dictionary of methods with no coordinate values</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>True False 40</x:v>
+        <x:v>A tuple such as `(17.3850, 78.4867)`</x:v>
       </x:c>
       <x:c r="P39" t="str">
-        <x:v>False True 40</x:v>
+        <x:v>Separate classes for latitude and longitude</x:v>
       </x:c>
       <x:c r="Q39" t="n">
-        <x:v>4</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>Python - MCQ - 9.4.9</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>A thermostat must store a target temperature and refuse values outside a safe range. Which design best keeps the data and rule together?</x:v>
+        <x:v>Registration must protect an event's capacity
+An event has a title, capacity, and current registrations. Every registration must be rejected once capacity is reached, and hundreds of events follow the same rule independently. Which model best fits?</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>A `Thermostat` class can store the current target and expose a method that validates changes before updating it. This places the rule beside the state it protects.</x:v>
+        <x:v>A class lets every event retain independent state while reusing one capacity-enforcing registration method.</x:v>
       </x:c>
       <x:c r="D40" t="n">
         <x:v>1</x:v>
@@ -2636,7 +2581,7 @@
         <x:v>medium</x:v>
       </x:c>
       <x:c r="G40" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H40" t="str">
         <x:v>python - Set 4</x:v>
@@ -2652,38 +2597,31 @@
       </x:c>
       <x:c r="L40"/>
       <x:c r="M40" t="str">
-        <x:v>A Thermostat class with a target attribute and a validated update method</x:v>
+        <x:v>Store only all event titles in one tuple</x:v>
       </x:c>
       <x:c r="N40" t="str">
-        <x:v>A global target variable changed directly from every part of the program</x:v>
+        <x:v>Use unrelated variables and repeat the capacity condition at every registration call site in the application</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Two unrelated lists, one for targets and one for valid ranges</x:v>
+        <x:v>Keep a dictionary of capacities but omit registration behaviour</x:v>
       </x:c>
       <x:c r="P40" t="str">
-        <x:v>A string containing the target and the rule as plain text</x:v>
+        <x:v>Use an `Event` class with state and a registration method that enforces the limit</x:v>
       </x:c>
       <x:c r="Q40" t="n">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="39.599998474121094" hidden="0" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>Python - MCQ - 9.4.10</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>An order should store both its code and quantity, but object creation fails.
-```python
-class Order:
-    def __init__(code, quantity):
-        code.value = code
-        code.quantity = quantity
-o = Order('A7', 3)
-```
-Which revision correctly fixes the constructor?</x:v>
+        <x:v>Choosing the point where a class earns its place
+Version A represents each student as a dictionary, while several screens independently implement pass, grade, and report rules. Version B uses `Student` objects with those operations as methods. The system will manage thousands of students and revise grading rules annually. Which judgment is most defensible?</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>The first constructor parameter must receive the new object. Using `self` there and assigning the supplied values to `self.code` and `self.quantity` stores both attributes correctly.</x:v>
+        <x:v>The class centralises recurring rules for reuse while keeping every student's attribute values independent.</x:v>
       </x:c>
       <x:c r="D41" t="n">
         <x:v>1</x:v>
@@ -2695,7 +2633,7 @@
         <x:v>hard</x:v>
       </x:c>
       <x:c r="G41" t="str">
-        <x:v>analyze</x:v>
+        <x:v>evaluate</x:v>
       </x:c>
       <x:c r="H41" t="str">
         <x:v>python - Set 4</x:v>
@@ -2707,20 +2645,21 @@
         <x:v>object-oriented-programming-intro</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>constructors</x:v>
+        <x:v>modeling-with-classes</x:v>
       </x:c>
       <x:c r="L41"/>
       <x:c r="M41" t="str">
-        <x:v>`def __init__(code, quantity): return quantity`</x:v>
+        <x:v>Version A is preferable because repeated rules become safer as the number of screens grows</x:v>
       </x:c>
       <x:c r="N41" t="str">
-        <x:v>`def __init__(self, code, quantity): self.code = code; self.quantity = quantity`</x:v>
+        <x:v>Version B better centralises shared behaviour while each object retains its own student data</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>`def __init__(): code = 'A7'`</x:v>
+        <x:v>Both designs are equivalent because a dictionary automatically supplies the same methods as a class</x:v>
       </x:c>
       <x:c r="P41" t="str">
-        <x:v>`def Order(self, code, quantity): self = code`</x:v>
+        <x:v>Neither design can represent more than one student at a time
+---</x:v>
       </x:c>
       <x:c r="Q41" t="n">
         <x:v>2</x:v>
